--- a/public/examples/import_contacts_exemple.xlsx
+++ b/public/examples/import_contacts_exemple.xlsx
@@ -516,7 +516,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>12345678901234</v>
+        <v>55566677788899</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
@@ -536,7 +536,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>98765432109876</v>
+        <v>99988877766655</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -556,7 +556,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>11122233344455</v>
+        <v>44433322211100</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
